--- a/docs/all/01_TablasDescriptivas/idx9_infnin_summary_labels.xlsx
+++ b/docs/all/01_TablasDescriptivas/idx9_infnin_summary_labels.xlsx
@@ -406,10 +406,10 @@
         <v>125</v>
       </c>
       <c r="D2">
-        <v>-3.701348843348703</v>
+        <v>-3.701348843348702</v>
       </c>
       <c r="E2">
-        <v>12.7686421710282</v>
+        <v>12.76864217102822</v>
       </c>
       <c r="F2">
         <v>-73.83531535774559</v>
@@ -436,7 +436,7 @@
         <v>-10.6345295487201</v>
       </c>
       <c r="E3">
-        <v>4.087776876592734</v>
+        <v>4.087776876592733</v>
       </c>
       <c r="F3">
         <v>-26.92307692307692</v>
@@ -463,7 +463,7 @@
         <v>-325.3657217778798</v>
       </c>
       <c r="E4">
-        <v>267.0718035148934</v>
+        <v>267.0718035148935</v>
       </c>
       <c r="F4">
         <v>-1808.225352568757</v>
@@ -490,7 +490,7 @@
         <v>-6.75183814651126</v>
       </c>
       <c r="E5">
-        <v>3.518242635300806</v>
+        <v>3.518242635300807</v>
       </c>
       <c r="F5">
         <v>-16.3265306122449</v>
@@ -517,7 +517,7 @@
         <v>-7.31118074806366</v>
       </c>
       <c r="E6">
-        <v>14.57222173604013</v>
+        <v>14.57222173604012</v>
       </c>
       <c r="F6">
         <v>-82.30452674897118</v>
@@ -652,7 +652,7 @@
         <v>-10.86807998657227</v>
       </c>
       <c r="E11">
-        <v>3.28915659740719</v>
+        <v>3.289156597407191</v>
       </c>
       <c r="F11">
         <v>-22.09000015258789</v>
